--- a/paper_trading_lay0x1/sinais_lay0x1_realista_2026-07-16.xlsx
+++ b/paper_trading_lay0x1/sinais_lay0x1_realista_2026-07-16.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sinais" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,21 @@
           <t>Estratégia</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro (R$)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Placar Final</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +522,19 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Random Forest (RF)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2-1</t>
         </is>
       </c>
     </row>
